--- a/images/images3.xlsx
+++ b/images/images3.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{45B90545-229D-46C1-BEEC-D92347E563A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ABC6717-067E-430D-98F5-1925A582CFF9}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{45B90545-229D-46C1-BEEC-D92347E563A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E98B539-BF09-463E-B506-30EE3F74A2A5}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11295" xr2:uid="{5B834B4D-96A9-4FB9-ABD8-2D18CF441BD9}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{5B834B4D-96A9-4FB9-ABD8-2D18CF441BD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,6 +85,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF364354"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -101,21 +107,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>17127</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>49691</xdr:rowOff>
+      <xdr:colOff>84857</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>6334</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="グループ化 1">
+        <xdr:cNvPr id="177" name="グループ化 176">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D377499-D0CC-476A-B525-30867BCEE96D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B027036B-F145-2D96-1BBA-7459A2E60846}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -123,18 +129,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="685800" y="238125"/>
-          <a:ext cx="3446127" cy="1954691"/>
-          <a:chOff x="6142500" y="2876608"/>
-          <a:chExt cx="3444799" cy="1990532"/>
+          <a:off x="684944" y="4473539"/>
+          <a:ext cx="3509576" cy="2360829"/>
+          <a:chOff x="686210" y="4475726"/>
+          <a:chExt cx="3515905" cy="2361979"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="3" name="グループ化 2">
+          <xdr:cNvPr id="119" name="グループ化 118">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48159C5-8F30-31E1-8D41-5714A7EA6567}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5768893A-29E6-C088-7391-9E4462FC8B20}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -142,18 +148,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="6142500" y="2876608"/>
-            <a:ext cx="2826532" cy="1990532"/>
+            <a:off x="753940" y="4903498"/>
+            <a:ext cx="2829260" cy="1934207"/>
             <a:chOff x="1373409" y="5000625"/>
             <a:chExt cx="2842620" cy="1972140"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="12" name="グループ化 11">
+            <xdr:cNvPr id="158" name="グループ化 157">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD80205-E51A-AC7C-6B58-C6229DCB71C5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6357FAFA-B3FD-40CE-BE04-64B964FB799A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -169,10 +175,10 @@
           </xdr:grpSpPr>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="14" name="図 13">
+              <xdr:cNvPr id="160" name="図 159">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22573EDE-0722-79A4-B810-204608CCCD55}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26FA6ED9-735B-C3D0-54DC-D5699B7B40FB}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -203,10 +209,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="15" name="図 14">
+              <xdr:cNvPr id="161" name="図 160">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{299BCB54-0D5B-8C55-DFFE-FEDD8DDB5607}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34A4EDDA-F685-2EDB-E542-ADD38EDB5252}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -237,10 +243,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="16" name="図 15">
+              <xdr:cNvPr id="162" name="図 161">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25CFFF41-568A-98F1-45B6-69E8ED16CEEB}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE0B3C01-D117-7048-AFDB-CE2A28934BE5}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -271,10 +277,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="17" name="図 16">
+              <xdr:cNvPr id="163" name="図 162">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3026B85A-4624-382D-A58D-5F91A58999AD}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8A3BA11-C87B-1AEA-51D1-DC1114B38EA1}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -305,10 +311,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="18" name="図 17">
+              <xdr:cNvPr id="164" name="図 163">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A604FEB1-6872-00DF-0299-F6D8EBFBCF6A}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D160A543-2C32-964C-6CFC-394A43922530}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -339,10 +345,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="19" name="図 18">
+              <xdr:cNvPr id="165" name="図 164">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFDF8678-3C49-F6E3-FA67-6A5E2CD2CD08}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B709146-7A6A-8B88-8D83-9F3D116AE62A}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -373,10 +379,10 @@
           </xdr:pic>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="20" name="テキスト ボックス 19">
+              <xdr:cNvPr id="166" name="テキスト ボックス 165">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE565E77-19E5-9F4C-A8BF-E647230BD586}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B744CDF-8AA8-7BA8-5495-1F5209821810}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -454,10 +460,10 @@
           </xdr:sp>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="21" name="テキスト ボックス 20">
+              <xdr:cNvPr id="167" name="テキスト ボックス 166">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F6F49DC-D257-F167-F244-65173FE08A59}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00442CF1-BCB0-FB79-9A2E-023C69C9A172}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -537,10 +543,10 @@
           </xdr:sp>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="22" name="図 21">
+              <xdr:cNvPr id="168" name="図 167">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7CD80AB-E075-1B6F-DCE2-E298C14C5EE8}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{648AF84E-3050-B9F2-143B-15D3B7C0AD74}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -571,10 +577,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="23" name="図 22">
+              <xdr:cNvPr id="169" name="図 168">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79178CDC-966D-6987-5973-5769243A3070}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119C0E13-2754-5EC3-31FE-12F9F8159701}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -605,10 +611,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="24" name="図 23">
+              <xdr:cNvPr id="170" name="図 169">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C621D6-266C-FE4B-97B5-751DE9D2A0DD}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB06315-BE66-940D-9685-D402874DA529}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -639,10 +645,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="25" name="図 24">
+              <xdr:cNvPr id="171" name="図 170">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C934C7-119E-B073-D736-429CC1353EF5}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C28178D-D970-0C3C-7D0E-ADE2C182378B}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -673,10 +679,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="26" name="図 25">
+              <xdr:cNvPr id="172" name="図 171">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8033EB9-0FE8-D57F-D35A-446C7C7ED6CA}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{484F768F-4999-406F-7661-BE0F35583958}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -707,10 +713,10 @@
           </xdr:pic>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="27" name="図 26">
+              <xdr:cNvPr id="173" name="図 172">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6394A9-9A4C-7908-4AC3-044F90CF7BF5}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5948270-E0A1-35AD-A35B-34AB15705D42}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -741,10 +747,10 @@
           </xdr:pic>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="28" name="テキスト ボックス 27">
+              <xdr:cNvPr id="174" name="テキスト ボックス 173">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76591313-4EDC-743C-396E-EFACD9770147}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75D1F03A-6057-2949-DD65-7FCACDC4F7E1}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -804,10 +810,10 @@
           </xdr:sp>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="29" name="テキスト ボックス 28">
+              <xdr:cNvPr id="175" name="テキスト ボックス 174">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4086CB0-CFF2-FB4B-0A62-DF014C7D82F0}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A37276B9-5813-DB01-4378-369182620656}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -871,10 +877,10 @@
           </xdr:sp>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="30" name="テキスト ボックス 29">
+              <xdr:cNvPr id="176" name="テキスト ボックス 175">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C3421F0-0233-5BED-A6AD-D6E3D09A13A2}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB3DDEFD-4381-E3E5-DB17-5A3F91F9CA84}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -935,10 +941,10 @@
         </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="13" name="テキスト ボックス 12">
+            <xdr:cNvPr id="159" name="テキスト ボックス 158">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4102CD89-1CB7-8CC4-198F-3973CA1DD45F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{253F4A4E-9799-4268-E82E-415035F5BF23}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -999,10 +1005,10 @@
       </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="4" name="図 3">
+          <xdr:cNvPr id="120" name="図 119">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A551797B-B9C9-549B-F9B8-935CE5320ACF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E24A93BC-65D2-EEF7-8148-B10DEF391370}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1023,20 +1029,491 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6620685" y="2999613"/>
-            <a:ext cx="2034481" cy="329127"/>
+            <a:off x="1232309" y="5024288"/>
+            <a:ext cx="2036494" cy="320640"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="121" name="四角形: 角を丸くする 120">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C446A676-62B7-1684-3D7A-9A4E73B581A0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3289988" y="5183000"/>
+            <a:ext cx="912127" cy="1050720"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFD961"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="364354"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="122" name="テキスト ボックス 121">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2422E3EC-ABD1-74B1-8D2B-24A78F7F60CA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3414093" y="5982614"/>
+            <a:ext cx="663508" cy="227068"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>コンテナ</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="123" name="四角形: 角を丸くする 122">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD4F34E6-D55D-ECE5-4F98-59A2237A4D4C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3364396" y="5858685"/>
+            <a:ext cx="762903" cy="172123"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFD961"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="364354"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="124" name="四角形: 角を丸くする 123">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BFFB11A-8639-258C-AE67-9B3B4955CBBA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3364396" y="5646158"/>
+            <a:ext cx="762903" cy="172123"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFD961"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="364354"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="125" name="テキスト ボックス 124">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{393D2B07-9FB0-D9FA-3E08-AE0C225D1618}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3414093" y="5838939"/>
+            <a:ext cx="663508" cy="227069"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>ubuntsu</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="126" name="テキスト ボックス 125">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5417985A-EF9B-327C-A80C-D25C2A60AEF8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3317420" y="5623856"/>
+            <a:ext cx="856853" cy="227069"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>python3.10.10</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="138" name="テキスト ボックス 137">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF4346A5-6313-59B6-DD38-7018347F3E3B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="686210" y="4475726"/>
+            <a:ext cx="1493185" cy="409144"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1.</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>環境構築</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>618480</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>43357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>276530</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>136218</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="179" name="グループ化 178">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60DCD2CB-D784-A4A8-2813-9C802447ADA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="618480" y="749705"/>
+          <a:ext cx="10617151" cy="3153704"/>
+          <a:chOff x="618480" y="750051"/>
+          <a:chExt cx="10637405" cy="3154174"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="5" name="グループ化 4">
+          <xdr:cNvPr id="117" name="グループ化 116">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BA9CF8-0992-1F02-0B4D-CC5B591C2BBE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2472400-1A91-3953-4268-24E02835881F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1044,12 +1521,914 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="8676342" y="3163843"/>
-            <a:ext cx="910957" cy="619453"/>
-            <a:chOff x="3923109" y="5231747"/>
-            <a:chExt cx="914400" cy="618793"/>
+            <a:off x="618480" y="750051"/>
+            <a:ext cx="10637405" cy="3056535"/>
+            <a:chOff x="618480" y="750051"/>
+            <a:chExt cx="10637405" cy="3056535"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="3" name="グループ化 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48159C5-8F30-31E1-8D41-5714A7EA6567}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="686210" y="1177823"/>
+              <a:ext cx="2829260" cy="1934207"/>
+              <a:chOff x="1373409" y="5000625"/>
+              <a:chExt cx="2842620" cy="1972140"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="12" name="グループ化 11">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD80205-E51A-AC7C-6B58-C6229DCB71C5}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="1373409" y="5000625"/>
+                <a:ext cx="2842620" cy="1972140"/>
+                <a:chOff x="1373409" y="5000625"/>
+                <a:chExt cx="2842620" cy="1972140"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="14" name="図 13">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22573EDE-0722-79A4-B810-204608CCCD55}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1373409" y="6363165"/>
+                  <a:ext cx="2532462" cy="609600"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="15" name="図 14">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{299BCB54-0D5B-8C55-DFFE-FEDD8DDB5607}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="3171781" y="5794124"/>
+                  <a:ext cx="719406" cy="549991"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="16" name="図 15">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25CFFF41-568A-98F1-45B6-69E8ED16CEEB}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1377214" y="5000625"/>
+                  <a:ext cx="1775065" cy="1346743"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="17" name="図 16">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3026B85A-4624-382D-A58D-5F91A58999AD}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1490760" y="5329910"/>
+                  <a:ext cx="1572438" cy="913059"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="18" name="図 17">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A604FEB1-6872-00DF-0299-F6D8EBFBCF6A}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1509566" y="5982165"/>
+                  <a:ext cx="1510272" cy="296661"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="19" name="図 18">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFDF8678-3C49-F6E3-FA67-6A5E2CD2CD08}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1737481" y="6072879"/>
+                  <a:ext cx="1051874" cy="136072"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:sp macro="" textlink="">
+              <xdr:nvSpPr>
+                <xdr:cNvPr id="20" name="テキスト ボックス 19">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE565E77-19E5-9F4C-A8BF-E647230BD586}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvSpPr txBox="1"/>
+              </xdr:nvSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1588549" y="6072881"/>
+                  <a:ext cx="1357575" cy="233590"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln w="9525" cmpd="sng">
+                  <a:noFill/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="dk1"/>
+                </a:fontRef>
+              </xdr:style>
+              <xdr:txBody>
+                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:effectLst/>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:rPr>
+                    <a:t>Linux</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:effectLst/>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:rPr>
+                    <a:t>カーネル</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:endParaRPr>
+                </a:p>
+              </xdr:txBody>
+            </xdr:sp>
+            <xdr:sp macro="" textlink="">
+              <xdr:nvSpPr>
+                <xdr:cNvPr id="21" name="テキスト ボックス 20">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F6F49DC-D257-F167-F244-65173FE08A59}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvSpPr txBox="1"/>
+              </xdr:nvSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1607728" y="5957219"/>
+                  <a:ext cx="1357575" cy="247197"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln w="9525" cmpd="sng">
+                  <a:noFill/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="dk1"/>
+                </a:fontRef>
+              </xdr:style>
+              <xdr:txBody>
+                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>Linux</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t> </a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>(Ubuntsu)</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:endParaRPr>
+                </a:p>
+              </xdr:txBody>
+            </xdr:sp>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="22" name="図 21">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7CD80AB-E075-1B6F-DCE2-E298C14C5EE8}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1529312" y="5404084"/>
+                  <a:ext cx="288580" cy="246407"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="23" name="図 22">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79178CDC-966D-6987-5973-5769243A3070}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1509566" y="5650491"/>
+                  <a:ext cx="1036079" cy="296661"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="24" name="図 23">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C621D6-266C-FE4B-97B5-751DE9D2A0DD}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1689415" y="5736227"/>
+                  <a:ext cx="689711" cy="136072"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="25" name="図 24">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C934C7-119E-B073-D736-429CC1353EF5}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="1741602" y="5733687"/>
+                  <a:ext cx="614196" cy="165652"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="26" name="図 25">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8033EB9-0FE8-D57F-D35A-446C7C7ED6CA}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="2572493" y="5399170"/>
+                  <a:ext cx="441198" cy="556194"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:pic>
+              <xdr:nvPicPr>
+                <xdr:cNvPr id="27" name="図 26">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6394A9-9A4C-7908-4AC3-044F90CF7BF5}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvPicPr>
+                  <a:picLocks noChangeAspect="1"/>
+                </xdr:cNvPicPr>
+              </xdr:nvPicPr>
+              <xdr:blipFill rotWithShape="1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="email">
+                  <a:extLst>
+                    <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                      <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                    </a:ext>
+                  </a:extLst>
+                </a:blip>
+                <a:srcRect/>
+                <a:stretch/>
+              </xdr:blipFill>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="2613344" y="5546971"/>
+                  <a:ext cx="326814" cy="238125"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+              </xdr:spPr>
+            </xdr:pic>
+            <xdr:sp macro="" textlink="">
+              <xdr:nvSpPr>
+                <xdr:cNvPr id="28" name="テキスト ボックス 27">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76591313-4EDC-743C-396E-EFACD9770147}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvSpPr txBox="1"/>
+              </xdr:nvSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="2850283" y="5949320"/>
+                  <a:ext cx="1357575" cy="247197"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln w="9525" cmpd="sng">
+                  <a:noFill/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="dk1"/>
+                </a:fontRef>
+              </xdr:style>
+              <xdr:txBody>
+                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>VS Code</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:endParaRPr>
+                </a:p>
+              </xdr:txBody>
+            </xdr:sp>
+            <xdr:sp macro="" textlink="">
+              <xdr:nvSpPr>
+                <xdr:cNvPr id="29" name="テキスト ボックス 28">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4086CB0-CFF2-FB4B-0A62-DF014C7D82F0}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvSpPr txBox="1"/>
+              </xdr:nvSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="2858454" y="6138178"/>
+                  <a:ext cx="1357575" cy="233590"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln w="9525" cmpd="sng">
+                  <a:noFill/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="dk1"/>
+                </a:fontRef>
+              </xdr:style>
+              <xdr:txBody>
+                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:effectLst/>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:rPr>
+                    <a:t>Windows11</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:endParaRPr>
+                </a:p>
+              </xdr:txBody>
+            </xdr:sp>
+            <xdr:sp macro="" textlink="">
+              <xdr:nvSpPr>
+                <xdr:cNvPr id="30" name="テキスト ボックス 29">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C3421F0-0233-5BED-A6AD-D6E3D09A13A2}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvSpPr txBox="1"/>
+              </xdr:nvSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="2361042" y="5572590"/>
+                  <a:ext cx="861483" cy="247197"/>
+                </a:xfrm>
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln w="9525" cmpd="sng">
+                  <a:noFill/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="dk1"/>
+                </a:fontRef>
+              </xdr:style>
+              <xdr:txBody>
+                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>Server</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:endParaRPr>
+                </a:p>
+              </xdr:txBody>
+            </xdr:sp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="13" name="テキスト ボックス 12">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4102CD89-1CB7-8CC4-198F-3973CA1DD45F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2360237" y="5476875"/>
+                <a:ext cx="860667" cy="247197"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>VS Code</a:t>
+                </a:r>
+                <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="図 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A551797B-B9C9-549B-F9B8-935CE5320ACF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect l="42737" b="68425"/>
+            <a:stretch/>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1164579" y="1298613"/>
+              <a:ext cx="2036494" cy="320640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="四角形: 角を丸くする 5">
@@ -1063,8 +2442,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3923109" y="5231747"/>
-              <a:ext cx="914400" cy="595313"/>
+              <a:off x="3222258" y="1457325"/>
+              <a:ext cx="912127" cy="1050720"/>
             </a:xfrm>
             <a:prstGeom prst="roundRect">
               <a:avLst/>
@@ -1116,8 +2495,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4047635" y="5616950"/>
-              <a:ext cx="665349" cy="233590"/>
+              <a:off x="3346363" y="2256939"/>
+              <a:ext cx="663508" cy="227068"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1183,8 +2562,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3997769" y="5490883"/>
-              <a:ext cx="765081" cy="175092"/>
+              <a:off x="3296666" y="2133010"/>
+              <a:ext cx="762903" cy="172123"/>
             </a:xfrm>
             <a:prstGeom prst="roundRect">
               <a:avLst/>
@@ -1236,8 +2615,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3997769" y="5272085"/>
-              <a:ext cx="765081" cy="175092"/>
+              <a:off x="3296666" y="1920483"/>
+              <a:ext cx="762903" cy="172123"/>
             </a:xfrm>
             <a:prstGeom prst="roundRect">
               <a:avLst/>
@@ -1289,8 +2668,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4047635" y="5468192"/>
-              <a:ext cx="665349" cy="233590"/>
+              <a:off x="3346363" y="2113264"/>
+              <a:ext cx="663508" cy="227069"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1356,8 +2735,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3950634" y="5249398"/>
-              <a:ext cx="859350" cy="233590"/>
+              <a:off x="3249690" y="1898181"/>
+              <a:ext cx="856853" cy="227069"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1410,29 +2789,1669 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="48" name="図 47" descr="画像が生成されました">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6086F4FC-F4BA-4450-8B8E-E8916F948DE2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="4217424" y="2219018"/>
+              <a:ext cx="467122" cy="594953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="50" name="グループ化 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA12F749-D919-4344-A2AD-FBCD15B3E77A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="4814872" y="2254501"/>
+              <a:ext cx="649631" cy="480959"/>
+              <a:chOff x="6448425" y="600076"/>
+              <a:chExt cx="2541610" cy="1792708"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="51" name="図 50">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD13B5D-5DA1-AD4D-9FF5-F31F3392C676}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6448425" y="600076"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="52" name="図 51">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{282AA4D1-48D7-776D-3EFF-7C17610B2B8B}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6600825" y="752476"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="53" name="図 52">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634D3816-37ED-8C9C-945B-05CAAD5B0196}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6753225" y="904876"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="54" name="図 53">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECC93D4F-AB44-CB47-D777-7E307E6ECBBC}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6905625" y="1057276"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="55" name="図 54">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94F2BD12-4349-9747-EF41-D7268A1CF3C9}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7058026" y="1209675"/>
+                <a:ext cx="1932009" cy="1183109"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="65" name="図 64" descr="画像が生成されました">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8D9221C-7D52-4B2E-831F-4E3C38615B5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="3306813" y="1520908"/>
+              <a:ext cx="305210" cy="385428"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="66" name="グループ化 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{269ED6FB-77DB-4150-829E-ABDEA46A5355}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="3637915" y="1521785"/>
+              <a:ext cx="394147" cy="370779"/>
+              <a:chOff x="6448425" y="600076"/>
+              <a:chExt cx="2541611" cy="1792708"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="67" name="図 66">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C54FAAF9-D310-DFF9-3D47-B45D7B844884}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6448425" y="600076"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="68" name="図 67">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D3580D9-B85E-C10B-E48E-8F997AFB5E91}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6600825" y="752476"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="69" name="図 68">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17F9C420-889C-A172-6ACF-0121F3898084}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6753225" y="904876"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="70" name="図 69">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D846E0-43AB-5655-CF2C-042937719540}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6905625" y="1057276"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="71" name="図 70">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED294CA-48B7-4A78-33D9-CFF20326EA95}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7058025" y="1209676"/>
+                <a:ext cx="1932011" cy="1183108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="73" name="直線コネクタ 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00B26BA6-EB42-611B-F158-B57F7C60ED69}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="65" idx="3"/>
+              <a:endCxn id="91" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3612023" y="1540133"/>
+              <a:ext cx="1831652" cy="173489"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="364354"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="76" name="直線コネクタ 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B59F9671-6280-4FCB-AFDC-A063C2DB6227}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="71" idx="3"/>
+              <a:endCxn id="91" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="4032062" y="1540133"/>
+              <a:ext cx="1411613" cy="230082"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="364354"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="89" name="図 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E0EF63B-CDFF-2973-E6E9-D4AB056FF613}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+              <a:clrChange>
+                <a:clrFrom>
+                  <a:srgbClr val="FEFAF2"/>
+                </a:clrFrom>
+                <a:clrTo>
+                  <a:srgbClr val="FEFAF2">
+                    <a:alpha val="0"/>
+                  </a:srgbClr>
+                </a:clrTo>
+              </a:clrChange>
+            </a:blip>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4540319" y="2423308"/>
+              <a:ext cx="544215" cy="531369"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="91" name="テキスト ボックス 90">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4509009-FAF4-4E98-8EC2-ADF90B045F6F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5443675" y="1339135"/>
+              <a:ext cx="3933747" cy="401996"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>2.</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>情報（銘柄のリストとチャート）収集</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="96" name="テキスト ボックス 95">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F218C64-32C6-4EF0-B70D-6311D3EF6B2E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5443675" y="3204867"/>
+              <a:ext cx="1974306" cy="398903"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>4.</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>目視による厳選</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="97" name="テキスト ボックス 96">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21174175-BA90-4679-9CDF-E02C3DB445B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9247439" y="845892"/>
+              <a:ext cx="2008446" cy="567495"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l">
+                <a:lnSpc>
+                  <a:spcPts val="1680"/>
+                </a:lnSpc>
+              </a:pPr>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>銘柄が厳選されていく</a:t>
+              </a:r>
+              <a:br>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+              </a:br>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>イメージ（選定件数）</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="99" name="テキスト ボックス 98">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31B8760E-9F23-4EDC-BDDD-92756486EB5C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5443675" y="2170612"/>
+              <a:ext cx="4212106" cy="762910"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>3.</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>プログラム作成・実行</a:t>
+              </a:r>
+              <a:br>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+              </a:br>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>　  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>出来高・株価・チャートでスクリーニング</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="101" name="テキスト ボックス 100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AF8B249-1316-4005-A8EC-141CE89A961B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="618480" y="750051"/>
+              <a:ext cx="1493185" cy="409144"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>1.</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>環境構築</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="106" name="図 105">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0AEF5A2-B4BA-4D67-912E-9A8E9EA2C192}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect l="42737" b="68425"/>
+            <a:stretch/>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm rot="784330">
+              <a:off x="4191032" y="1853226"/>
+              <a:ext cx="1003496" cy="371736"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="110" name="グループ化 109">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33E47235-F1A3-040A-D426-F458BB7CF3D0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="4235543" y="3103425"/>
+              <a:ext cx="1182573" cy="703161"/>
+              <a:chOff x="4235543" y="3277539"/>
+              <a:chExt cx="1182573" cy="703161"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="100" name="図 99">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{254D2FD1-7EDA-DE5D-F2F6-29E76E1D6299}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="4235543" y="3277539"/>
+                <a:ext cx="1170361" cy="703161"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="109" name="図 108">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B5C0BF1-CCBD-41C7-B0BD-665E52C40E93}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="5239013" y="3334536"/>
+                <a:ext cx="179103" cy="264060"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="112" name="直線コネクタ 111">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF3FE18-A467-4F35-99BF-ACC7EFDD2E8E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="5489682" y="1331454"/>
+              <a:ext cx="5580000" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="364354"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="113" name="テキスト ボックス 112">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0C9C690-F846-447D-8BEF-BC675834ADB9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9450786" y="1438693"/>
+              <a:ext cx="1686680" cy="352056"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l">
+                <a:lnSpc>
+                  <a:spcPts val="1680"/>
+                </a:lnSpc>
+              </a:pPr>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>約</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>2500</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件～</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>4400</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="114" name="テキスト ボックス 113">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B82ED9D-BF61-4200-AA09-7568B6484874}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5443675" y="845892"/>
+              <a:ext cx="2008446" cy="567495"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l">
+                <a:lnSpc>
+                  <a:spcPts val="1680"/>
+                </a:lnSpc>
+              </a:pPr>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>選定ステップ</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="115" name="テキスト ボックス 114">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C569BA03-3280-49C0-802B-52134273CBE1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9450786" y="2256818"/>
+              <a:ext cx="1323467" cy="353644"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l">
+                <a:lnSpc>
+                  <a:spcPts val="1680"/>
+                </a:lnSpc>
+              </a:pPr>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>約</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>100</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>～</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>150</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="116" name="テキスト ボックス 115">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502010A0-066C-4A01-8B6E-7028CC9C5BF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9450786" y="3310508"/>
+              <a:ext cx="1200563" cy="353644"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l">
+                <a:lnSpc>
+                  <a:spcPts val="1680"/>
+                </a:lnSpc>
+              </a:pPr>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>約</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>3</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
       </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="178" name="正方形/長方形 177">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4066A06C-0D30-42D9-A239-BE363C2D83A9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4168468" y="3062785"/>
+            <a:ext cx="6882580" cy="841440"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:alpha val="70000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>316043</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>18906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>121504</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>522015</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>215081</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="181" name="右中かっこ 180">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45DA9A00-C431-F1D2-0B6A-00875C75D1E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11295398" y="5073301"/>
+          <a:ext cx="205972" cy="1399603"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 59946"/>
+            <a:gd name="adj2" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="364354"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>68543</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>163871</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>538251</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>50705</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30" descr="画像が生成されました">
+        <xdr:cNvPr id="182" name="図 181" descr="画像が生成されました">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD54D401-8113-4E58-8414-46E0BA141981}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24D58CF9-1A49-4269-BA01-5B159D4DF374}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1448,15 +4467,15 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="5517" t="5764" b="3161"/>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4800600" y="1666875"/>
-          <a:ext cx="838200" cy="1074004"/>
+          <a:off x="6244430" y="4977581"/>
+          <a:ext cx="469708" cy="608890"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1475,25 +4494,623 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>675969</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>489841</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>29494</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>358855</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>124044</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="204" name="グループ化 203">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{074EEF5B-B80D-E02F-F6E1-7DC71B4B3C6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6155520" y="5538481"/>
+          <a:ext cx="1052773" cy="707248"/>
+          <a:chOff x="6165646" y="5658910"/>
+          <a:chExt cx="1055306" cy="722957"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="186" name="図 185">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA03CCA-2D57-4C01-B2D0-C270FA1AE3E1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6869042" y="5697402"/>
+            <a:ext cx="351910" cy="684465"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="183" name="図 182">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E84A82D9-EA5E-495F-8B48-502C9E538FF1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6165646" y="5697402"/>
+            <a:ext cx="264158" cy="684465"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="184" name="図 183">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E52AC44-6845-4292-A6ED-02703A9726F1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6213534" y="5740763"/>
+            <a:ext cx="829553" cy="545871"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="185" name="図 184">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13BD25C5-BA60-4233-98E2-DA4362981DFB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print">
+            <a:clrChange>
+              <a:clrFrom>
+                <a:srgbClr val="FEFEFB"/>
+              </a:clrFrom>
+              <a:clrTo>
+                <a:srgbClr val="FEFEFB">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:clrTo>
+            </a:clrChange>
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6826830" y="5970483"/>
+            <a:ext cx="390735" cy="406290"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="187" name="図 186">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7145B9D3-4C58-41AE-8468-B6D27C81088F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6213229" y="5658910"/>
+            <a:ext cx="731714" cy="180447"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="188" name="図 187">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5287498C-E6B7-411B-B5D6-B871D4D181D7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6797289" y="6240391"/>
+            <a:ext cx="245310" cy="46194"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>347830</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>238896</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>221101</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>14074</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="189" name="テキスト ボックス 188">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E8A1DCD-5904-4937-8B59-E0609EEB1F6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7209927" y="5052606"/>
+          <a:ext cx="3304319" cy="497234"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3-1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>出来高・株価でスクリーニング</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>347830</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>39648</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>572479</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>55511</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="190" name="テキスト ボックス 189">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D13D863B-D800-4DA6-AC94-7D3D24B4C368}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7209927" y="5816100"/>
+          <a:ext cx="4341907" cy="497234"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3-2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>チャートを取得した銘柄を</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>OCR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>で一覧にする</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>556516</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>46153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>62016</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="191" name="テキスト ボックス 190">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AC4784-519B-43F5-8F0E-DAFFFA7C235C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11535871" y="5581919"/>
+          <a:ext cx="2442323" cy="497234"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3-3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>データを突合させる</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>108085</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>34453</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>655784</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95352</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図 35">
+        <xdr:cNvPr id="194" name="図 193">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26038A4F-0287-B59D-4FEE-15C9E4B3428F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D62F6B41-D7CC-454F-BA48-57F9F67527F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1502,15 +5119,1918 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FEFAF2"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FEFAF2">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6448425" y="600075"/>
-          <a:ext cx="2956816" cy="1810669"/>
+          <a:off x="8376596" y="7573389"/>
+          <a:ext cx="547699" cy="547282"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2" descr="画像が生成されました">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D5E02C-C78A-4763-6692-6A9CE1863513}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6172200" y="7858125"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13320</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>177502</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>678909</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>172262</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="199" name="グループ化 198">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC444383-F1E7-668B-7174-844FBEDECC20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="698264" y="7240985"/>
+          <a:ext cx="6145139" cy="701108"/>
+          <a:chOff x="702363" y="7473247"/>
+          <a:chExt cx="6177929" cy="724334"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="193" name="図 192" descr="画像が生成されました">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5D075E0-9FBE-4C5D-8F55-8D55C1B4D99A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="702363" y="7516452"/>
+            <a:ext cx="467122" cy="612767"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="196" name="図 195">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D9E36C-BE59-DF64-532C-09CC50B642D4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1577673" y="7515336"/>
+            <a:ext cx="757635" cy="614999"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="197" name="テキスト ボックス 196">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{553BC5C3-4E05-43EE-B17E-3D9959A36808}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1104496" y="7473247"/>
+            <a:ext cx="577579" cy="699176"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>＋</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="198" name="テキスト ボックス 197">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFE67FFE-66B4-4154-ACDF-C5DCF04AC2B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2573775" y="7488273"/>
+            <a:ext cx="4306517" cy="709308"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>収集した銘柄一覧に</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>yfinance</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>で出来高などのデータを結合して絞り込み</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>30400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>235565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>68119</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>66573</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="216" name="グループ化 215">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{114623B8-53CF-D529-C8BB-C96A6FD7401A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="715344" y="8240846"/>
+          <a:ext cx="4147382" cy="1008255"/>
+          <a:chOff x="713325" y="8484574"/>
+          <a:chExt cx="4135266" cy="1044098"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="215" name="グループ化 214">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65AF9A26-B592-EC13-96B8-64D1906A61E1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="713325" y="8491627"/>
+            <a:ext cx="1154729" cy="1037045"/>
+            <a:chOff x="713325" y="8491627"/>
+            <a:chExt cx="1154729" cy="1037045"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="200" name="図 199">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F35B93B4-983B-3CA5-52C2-492FC0AE8011}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="713325" y="8491627"/>
+              <a:ext cx="1154729" cy="705438"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="201" name="テキスト ボックス 200">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0724BD41-7852-442E-AC28-8DB80F511660}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="928750" y="9145855"/>
+              <a:ext cx="723880" cy="382817"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>白黒化</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="214" name="グループ化 213">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{165518AA-51BA-57D3-298B-2C1A48982E2F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2288692" y="8578683"/>
+            <a:ext cx="1090526" cy="938519"/>
+            <a:chOff x="1886976" y="8578683"/>
+            <a:chExt cx="1090526" cy="938519"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="202" name="図 201">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C424A817-0797-E9D9-1250-C526382B2493}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2158267" y="8578683"/>
+              <a:ext cx="547945" cy="572292"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="203" name="テキスト ボックス 202">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73DBDB41-767F-4396-8958-9174D984BF99}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1886976" y="9134385"/>
+              <a:ext cx="1090526" cy="382817"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>トリミング</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="213" name="グループ化 212">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ED61F5C-C20D-886D-53AF-5DDDC8B03D33}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3799855" y="8484574"/>
+            <a:ext cx="1048736" cy="1023613"/>
+            <a:chOff x="3161859" y="8484574"/>
+            <a:chExt cx="1048736" cy="1023613"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="205" name="グループ化 204">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EBC760B-F541-4FDC-90AD-ADB9DF3C0721}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="3161859" y="8484574"/>
+              <a:ext cx="1048736" cy="728754"/>
+              <a:chOff x="6165646" y="5658910"/>
+              <a:chExt cx="1055306" cy="722957"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="206" name="図 205">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2620237D-D051-1E27-FB3D-C0D7DE04E87B}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr bwMode="auto">
+              <a:xfrm>
+                <a:off x="6869042" y="5697402"/>
+                <a:ext cx="351910" cy="684465"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:extLst>
+                <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                  <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                  </a14:hiddenFill>
+                </a:ext>
+              </a:extLst>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="207" name="図 206">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B859B3F8-8288-8607-2366-A095FBB45676}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr bwMode="auto">
+              <a:xfrm>
+                <a:off x="6165646" y="5697402"/>
+                <a:ext cx="264158" cy="684465"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:extLst>
+                <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                  <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                  </a14:hiddenFill>
+                </a:ext>
+              </a:extLst>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="208" name="図 207">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC3DBFE-1EB0-10E6-2BDD-07A9FF46BBBB}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6213534" y="5740763"/>
+                <a:ext cx="829553" cy="545871"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="209" name="図 208">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43CACFCC-FE7A-AE78-AF4C-E2D342A5A634}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+                <a:clrChange>
+                  <a:clrFrom>
+                    <a:srgbClr val="FEFEFB"/>
+                  </a:clrFrom>
+                  <a:clrTo>
+                    <a:srgbClr val="FEFEFB">
+                      <a:alpha val="0"/>
+                    </a:srgbClr>
+                  </a:clrTo>
+                </a:clrChange>
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr bwMode="auto">
+              <a:xfrm>
+                <a:off x="6826830" y="5970483"/>
+                <a:ext cx="390735" cy="406290"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:extLst>
+                <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                  <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                  </a14:hiddenFill>
+                </a:ext>
+              </a:extLst>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="210" name="図 209">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{223573FB-5A2E-A960-2B11-CDDDA85C1B50}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6213229" y="5658910"/>
+                <a:ext cx="731714" cy="180447"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="211" name="図 210">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC284019-5C12-5AC7-DD5A-40198387C208}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6797289" y="6240391"/>
+                <a:ext cx="245310" cy="46194"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="212" name="テキスト ボックス 211">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AE31F36-6AE3-4AF8-83B8-34AE4C76867A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3431519" y="9163881"/>
+              <a:ext cx="509418" cy="344306"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>OCR</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>260589</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>213269</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="1049" name="グループ化 1048">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A378725-DB0D-404B-75B2-EBD30FC35384}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3424719" y="9653427"/>
+          <a:ext cx="4370252" cy="3274112"/>
+          <a:chOff x="3413827" y="9676726"/>
+          <a:chExt cx="4357182" cy="3281499"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="1040" name="グループ化 1039">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84AE72EC-9EA2-640D-50E0-77A2D4C23852}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3413827" y="9676726"/>
+            <a:ext cx="4357182" cy="3281499"/>
+            <a:chOff x="3413827" y="9676726"/>
+            <a:chExt cx="4357182" cy="3281499"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="1027" name="グループ化 1026">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E375A47-6AED-EDB6-1D95-FA8920E505EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="3413827" y="9676726"/>
+              <a:ext cx="4357182" cy="3281499"/>
+              <a:chOff x="3413827" y="9676726"/>
+              <a:chExt cx="4357182" cy="3281499"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="218" name="図 217">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65329732-D6B4-FA78-70F8-EF0ABE0258EF}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27">
+                <a:extLst>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3422812" y="11227620"/>
+                <a:ext cx="4348197" cy="1721618"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="220" name="図 219">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B10CC887-B939-6D4A-FCC9-608F8C670BF1}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3413827" y="9676726"/>
+                <a:ext cx="4352579" cy="1579875"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="221" name="図 220">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2562866D-93D6-46A8-B2CB-6BFC1FEF3E3F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29">
+                <a:extLst>
+                  <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+                    <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                      <a14:imgLayer r:embed="rId30">
+                        <a14:imgEffect>
+                          <a14:artisticBlur/>
+                        </a14:imgEffect>
+                      </a14:imgLayer>
+                    </a14:imgProps>
+                  </a:ext>
+                  <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                    <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+                  </a:ext>
+                </a:extLst>
+              </a:blip>
+              <a:srcRect/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3431798" y="11699656"/>
+                <a:ext cx="997271" cy="1258569"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="222" name="正方形/長方形 221">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F337EFAA-1288-2FDE-F790-C8DBFF201346}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="4402113" y="9910358"/>
+                <a:ext cx="583919" cy="173116"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="28575">
+                <a:solidFill>
+                  <a:srgbClr val="EE0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="1024" name="正方形/長方形 1023">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C33740A-CC29-4F17-A37A-C169770AF04C}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="4554513" y="10081237"/>
+                <a:ext cx="825489" cy="173117"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="28575">
+                <a:solidFill>
+                  <a:srgbClr val="EE0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="1025" name="正方形/長方形 1024">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC09D60-136E-4ABE-BD0B-A2FE4120A9E0}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6008470" y="10080811"/>
+                <a:ext cx="822312" cy="173117"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="28575">
+                <a:solidFill>
+                  <a:srgbClr val="EE0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="1038" name="コネクタ: カギ線 1037">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{310CE7AF-16E3-4556-6393-A3EC4A118078}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="16200000" flipH="1">
+              <a:off x="6263580" y="10731058"/>
+              <a:ext cx="1224000" cy="89598"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -2120"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="EE0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="1043" name="正方形/長方形 1042">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3369FE1D-0BEE-4118-963D-D0D9727158B5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6684357" y="11404709"/>
+            <a:ext cx="485138" cy="139399"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="EE0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>680357</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>326754</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>90715</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="1063" name="グループ化 1062">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B15D5568-D466-873F-C6EC-0D86F53F089C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3420132" y="13420618"/>
+          <a:ext cx="5125948" cy="4799704"/>
+          <a:chOff x="3420132" y="13420618"/>
+          <a:chExt cx="5125948" cy="4799704"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="1052" name="図 1051">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8317FBA0-F8C6-DA20-2158-8DA9F3A2FDBF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3424719" y="13420618"/>
+            <a:ext cx="5121361" cy="1416014"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="1053" name="正方形/長方形 1052">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16DBBBE7-828C-4DD2-A42D-3C8C2764A4EA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5673421" y="13664496"/>
+            <a:ext cx="586097" cy="173116"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="EE0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="1054" name="正方形/長方形 1053">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27E9D14-1264-4F08-8225-52176AA9E468}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5766818" y="13835375"/>
+            <a:ext cx="827667" cy="172550"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="EE0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="1056" name="正方形/長方形 1055">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84A5CFE3-079F-421E-85D9-D9DF03AD7F20}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6628774" y="14607654"/>
+            <a:ext cx="1862694" cy="173965"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="EE0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="1057" name="図 1056">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FBD3019-30CD-449A-B47B-05E3F04A907A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3420132" y="14839795"/>
+            <a:ext cx="3682011" cy="3380527"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="1062" name="図 1061">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B5ECB4B-7266-4A33-A3F6-18F3C10A9851}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33">
+            <a:extLst>
+              <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+                <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a14:imgLayer r:embed="rId34">
+                    <a14:imgEffect>
+                      <a14:artisticPastelsSmooth/>
+                    </a14:imgEffect>
+                  </a14:imgLayer>
+                </a14:imgProps>
+              </a:ext>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3430473" y="15097196"/>
+            <a:ext cx="3679454" cy="3108474"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="1058" name="コネクタ: カギ線 1057">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84AEF8FB-0790-40E6-86F1-E82846044F74}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="1056" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="7004566" y="14756083"/>
+            <a:ext cx="529074" cy="580145"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="EE0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>513343</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>208363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A07B343-B8FF-4A57-09A4-C83CF9D45893}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="238125"/>
+          <a:ext cx="8057143" cy="9495238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>513343</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>208363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{155B4283-A84F-329F-2B40-F68DCC2B28D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="238125"/>
+          <a:ext cx="8057143" cy="9495238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>94381</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>208363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C88B6B-73C1-DCAA-F52F-0E56539F71A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="10001250"/>
+          <a:ext cx="6952381" cy="9495238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>94381</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>208363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF3A1CE-6BB1-44D1-EDF4-AB69A4434547}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="10001250"/>
+          <a:ext cx="6952381" cy="9495238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1826,4 +7346,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D557BC-1722-421C-8599-8F440CB62D8C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>